--- a/templates/samples/SHS_STOCK_SAMPLE.xlsx
+++ b/templates/samples/SHS_STOCK_SAMPLE.xlsx
@@ -445,13 +445,13 @@
         <v>350100000000000</v>
       </c>
       <c r="D2" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E2" t="str">
         <v>64GB</v>
       </c>
       <c r="F2" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G2" t="str">
         <v>GRAPHITE</v>
@@ -480,13 +480,13 @@
         <v>350100000095028</v>
       </c>
       <c r="D3" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E3" t="str">
         <v>256GB</v>
       </c>
       <c r="F3" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G3" t="str">
         <v>MIDNIGHT</v>
@@ -515,13 +515,13 @@
         <v>350100000190056</v>
       </c>
       <c r="D4" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E4" t="str">
         <v>64GB</v>
       </c>
       <c r="F4" t="str">
-        <v>Dual SIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G4" t="str">
         <v>GRAPHITE</v>
@@ -550,13 +550,13 @@
         <v>350100000285084</v>
       </c>
       <c r="D5" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E5" t="str">
         <v>256GB</v>
       </c>
       <c r="F5" t="str">
-        <v>eSIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G5" t="str">
         <v>MIDNIGHT</v>
@@ -585,13 +585,13 @@
         <v>350100000380112</v>
       </c>
       <c r="D6" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E6" t="str">
         <v>64GB</v>
       </c>
       <c r="F6" t="str">
-        <v>Dual SIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G6" t="str">
         <v>STARLIGHT</v>
@@ -620,7 +620,7 @@
         <v>350100000475140</v>
       </c>
       <c r="D7" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E7" t="str">
         <v>256GB</v>
@@ -661,7 +661,7 @@
         <v>64GB</v>
       </c>
       <c r="F8" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G8" t="str">
         <v>BLACK</v>
@@ -690,13 +690,13 @@
         <v>350100000665196</v>
       </c>
       <c r="D9" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E9" t="str">
         <v>256GB</v>
       </c>
       <c r="F9" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G9" t="str">
         <v>WHITE</v>

--- a/templates/samples/SHS_STOCK_SAMPLE.xlsx
+++ b/templates/samples/SHS_STOCK_SAMPLE.xlsx
@@ -442,7 +442,7 @@
         <v>IPHONE 12</v>
       </c>
       <c r="C2" t="str">
-        <v>350100000000000</v>
+        <v/>
       </c>
       <c r="D2" t="str">
         <v>Brand new</v>
@@ -477,7 +477,7 @@
         <v>IPHONE 14</v>
       </c>
       <c r="C3" t="str">
-        <v>350100000095028</v>
+        <v/>
       </c>
       <c r="D3" t="str">
         <v>ONU</v>
@@ -512,7 +512,7 @@
         <v>IPHONE 12</v>
       </c>
       <c r="C4" t="str">
-        <v>350100000190056</v>
+        <v/>
       </c>
       <c r="D4" t="str">
         <v>ONU</v>
@@ -547,7 +547,7 @@
         <v>IPHONE 14</v>
       </c>
       <c r="C5" t="str">
-        <v>350100000285084</v>
+        <v/>
       </c>
       <c r="D5" t="str">
         <v>B</v>
@@ -582,7 +582,7 @@
         <v>IPHONE 12</v>
       </c>
       <c r="C6" t="str">
-        <v>350100000380112</v>
+        <v/>
       </c>
       <c r="D6" t="str">
         <v>ONU</v>
@@ -617,7 +617,7 @@
         <v>IPHONE 14</v>
       </c>
       <c r="C7" t="str">
-        <v>350100000475140</v>
+        <v/>
       </c>
       <c r="D7" t="str">
         <v>C</v>
@@ -652,7 +652,7 @@
         <v>IPHONE 12</v>
       </c>
       <c r="C8" t="str">
-        <v>350100000570168</v>
+        <v/>
       </c>
       <c r="D8" t="str">
         <v>A</v>
@@ -687,7 +687,7 @@
         <v>IPHONE 14</v>
       </c>
       <c r="C9" t="str">
-        <v>350100000665196</v>
+        <v/>
       </c>
       <c r="D9" t="str">
         <v>ONU</v>
@@ -722,7 +722,7 @@
         <v>IPHONE 12</v>
       </c>
       <c r="C10" t="str">
-        <v>350100000760224</v>
+        <v/>
       </c>
       <c r="D10" t="str">
         <v>A</v>
@@ -757,7 +757,7 @@
         <v>IPHONE 14</v>
       </c>
       <c r="C11" t="str">
-        <v>350100000855252</v>
+        <v/>
       </c>
       <c r="D11" t="str">
         <v>A</v>
